--- a/test-files/gene-name-modifications/duplicate-gene-side-nonadjacent-output.xlsx
+++ b/test-files/gene-name-modifications/duplicate-gene-side-nonadjacent-output.xlsx
@@ -1,58 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="25915"/>
-  <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
-  <bookViews>
-    <workbookView xWindow="560" yWindow="560" windowWidth="25040" windowHeight="13620" tabRatio="500"/>
-  </bookViews>
+  <workbookPr codeName="ThisWorkbook" autoCompressPictures="false" showInkAnnotation="false"/>
   <sheets>
     <sheet name="network_optimized_weights" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="140000" concurrentCalc="0"/>
-  <extLst>
-    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{7523E5D3-25F3-A5E0-1632-64F254C22452}">
-      <mx:ArchID Flags="2"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="9">
-  <si>
-    <t>rows genes affected/cols genes controlling</t>
-  </si>
-  <si>
-    <t>a</t>
-  </si>
-  <si>
-    <t>duplicate</t>
-  </si>
-  <si>
-    <t>b</t>
-  </si>
-  <si>
-    <t>c</t>
-  </si>
-  <si>
-    <t>d</t>
-  </si>
-  <si>
-    <t>e</t>
-  </si>
-  <si>
-    <t>f</t>
-  </si>
-  <si>
-    <t>g</t>
-  </si>
-</sst>
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <numFmts count="1">
+    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+  </numFmts>
+  <fonts count="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -82,7 +65,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -413,42 +396,41 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I9"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
   <sheetData>
-    <row r="1" spans="1:9">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" t="s">
-        <v>1</v>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>cols regulators/rows targets</v>
+      </c>
+      <c r="B1" t="str">
+        <v>a</v>
+      </c>
+      <c r="C1" t="str">
+        <v>duplicate</v>
+      </c>
+      <c r="D1" t="str">
+        <v>b</v>
+      </c>
+      <c r="E1" t="str">
+        <v>c</v>
+      </c>
+      <c r="F1" t="str">
+        <v>d</v>
+      </c>
+      <c r="G1" t="str">
+        <v>e</v>
+      </c>
+      <c r="H1" t="str">
+        <v>f</v>
+      </c>
+      <c r="I1" t="str">
+        <v>g</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>a</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -475,9 +457,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
-      <c r="A3" t="s">
-        <v>2</v>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>duplicate</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -504,15 +486,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
-      <c r="A4" t="s">
-        <v>3</v>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>b</v>
       </c>
       <c r="B4">
         <v>0</v>
       </c>
       <c r="C4">
-        <v>9.7143193603914768E-2</v>
+        <v>0.09714319360391477</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -533,9 +515,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
-      <c r="A5" t="s">
-        <v>4</v>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>c</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -562,9 +544,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
-      <c r="A6" t="s">
-        <v>5</v>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>d</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -591,9 +573,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
-      <c r="A7" t="s">
-        <v>6</v>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>e</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -620,9 +602,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
-      <c r="A8" t="s">
-        <v>2</v>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>duplicate</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -649,9 +631,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
-      <c r="A9" t="s">
-        <v>7</v>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>f</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -679,11 +661,8 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <extLst>
-    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
-      <mx:PLV Mode="0" OnePage="0" WScale="0"/>
-    </ext>
-  </extLst>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:I9"/>
+  </ignoredErrors>
 </worksheet>
 </file>